--- a/游戏设计王/老虎机数学专题-连线彩金数学.xlsx
+++ b/游戏设计王/老虎机数学专题-连线彩金数学.xlsx
@@ -445,7 +445,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
@@ -454,6 +454,7 @@
     <numFmt numFmtId="177" formatCode="0.000%"/>
     <numFmt numFmtId="178" formatCode="0.0%"/>
     <numFmt numFmtId="179" formatCode="0.000%"/>
+    <numFmt numFmtId="180" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="33">
     <font>
@@ -1158,7 +1159,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1251,6 +1252,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="178" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="179" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" applyNumberFormat="1" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="180" applyNumberFormat="1" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="180" applyNumberFormat="1" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="180" applyNumberFormat="1" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="180" applyNumberFormat="1" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="180" applyNumberFormat="1" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="180" applyNumberFormat="1" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4901,11 +4909,11 @@
       <c r="B11" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="49">
         <f>SUM(C7:C10)</f>
         <v>0.01</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="49">
         <f>SUM(D7:D10)</f>
         <v>1</v>
       </c>
@@ -5019,15 +5027,15 @@
       <c r="A18" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="50">
         <f>B7*D7*$B$4</f>
         <v>0.05</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="50">
         <f>C7</f>
         <v>0.001</v>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="50">
         <f>B18+C18</f>
         <v>0.051</v>
       </c>
@@ -5039,15 +5047,15 @@
       <c r="A19" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="50">
         <f>B8*D8*$B$4</f>
         <v>0.02</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="50">
         <f>C8</f>
         <v>0.002</v>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="50">
         <f>B19+C19</f>
         <v>0.022</v>
       </c>
@@ -5059,15 +5067,15 @@
       <c r="A20" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="50">
         <f>B9*D9*$B$4</f>
         <v>0.002</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="50">
         <f>C9</f>
         <v>0.003</v>
       </c>
-      <c r="D20" s="12">
+      <c r="D20" s="50">
         <f>B20+C20</f>
         <v>0.005</v>
       </c>
@@ -5079,15 +5087,15 @@
       <c r="A21" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="50">
         <f>B10*D10*$B$4</f>
         <v>0.000775</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="50">
         <f>C10</f>
         <v>0.004</v>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="50">
         <f>B21+C21</f>
         <v>0.004775</v>
       </c>
@@ -5099,15 +5107,15 @@
       <c r="A22" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="B22" s="14">
+      <c r="B22" s="52">
         <f>SUM(B18:B21)</f>
         <v>0.072775</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="52">
         <f>SUM(C18:C21)</f>
         <v>0.01</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="52">
         <f>SUM(D18:D21)</f>
         <v>0.082775</v>
       </c>
@@ -5136,7 +5144,7 @@
       <c r="A24" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B24" s="12">
+      <c r="B24" s="50">
         <f>D22-E22</f>
         <v>-4.99999999999112e-6</v>
       </c>
